--- a/Book-Chapter/kuantum_programlama_ogrenci_gorev_dagilimi.xlsx
+++ b/Book-Chapter/kuantum_programlama_ogrenci_gorev_dagilimi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F7B0DC-9F6C-4C1C-B17E-21799BE3B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE74C796-F9CF-46DD-B0A8-D18659549082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="81">
   <si>
     <t>Bölüm</t>
   </si>
@@ -211,63 +211,9 @@
     <t>Görevli Öğrenci &amp; Ars Gor</t>
   </si>
   <si>
-    <t>5 sayfalık rapor (.docx veya .pdf) + 2 görsel (şema veya tarihsel zaman çizelgesi)</t>
-  </si>
-  <si>
-    <t>Teorik açıklama raporu (.pdf) + basit Python veya Qiskit kod örnekleri (.ipynb)</t>
-  </si>
-  <si>
-    <t>Metinsel rapor (.pdf) + Bloch küresi temsili görseli</t>
-  </si>
-  <si>
-    <t>Qiskit devre kodu (.ipynb) + Bloch küresi çıktısı + kısa açıklama</t>
-  </si>
-  <si>
     <t>Cirq veya Qiskit devre simülasyon kodu (.ipynb) + ekran çıktıları</t>
   </si>
   <si>
-    <t>Çalışan algoritma kodu (.ipynb) + sonuç raporu (.pdf)</t>
-  </si>
-  <si>
-    <t>Kod (.ipynb) + kod açıklama notları (.txt veya .pdf)</t>
-  </si>
-  <si>
-    <t>Kod (.ipynb) + algoritma sonuç tablosu + kısa değerlendirme raporu</t>
-  </si>
-  <si>
-    <t>Qiskit kodu (.ipynb) + çıktı ekran görüntüleri + yorum dosyası</t>
-  </si>
-  <si>
-    <t>Cirq kodu (.ipynb) + kuantum devre şeması (görsel) + açıklama belgesi</t>
-  </si>
-  <si>
-    <t>Kurulum rehberi (.pdf) + örnek çalışma kodu (.ipynb)</t>
-  </si>
-  <si>
-    <t>Üç algoritmanın kodları (.ipynb) + karşılaştırma tablosu (.xlsx veya .pdf)</t>
-  </si>
-  <si>
-    <t>Cirq devre kodu (.ipynb) + ekran çıktısı + açıklama notu</t>
-  </si>
-  <si>
-    <t>3 örnek devre kodu (.ipynb) + sonuç ekran görüntüleri</t>
-  </si>
-  <si>
-    <t>Q# kod dosyası (.qs) + VS Code ekran görüntüsü + kısa açıklama raporu</t>
-  </si>
-  <si>
-    <t>Karşılaştırma raporu (.pdf) + tablo (.xlsx)</t>
-  </si>
-  <si>
-    <t>Qiskit kodu (.ipynb) + örnek görsel çıktılar + açıklama raporu</t>
-  </si>
-  <si>
-    <t>QML modeli kodu (.ipynb) + sonuç grafikleri + açıklama raporu</t>
-  </si>
-  <si>
-    <t>Q# kodu (.qs) + uygulama çıktısı + protokol akış şeması</t>
-  </si>
-  <si>
     <t>Alfabetik sözlük (.docx) + ek açıklama notları</t>
   </si>
   <si>
@@ -278,6 +224,45 @@
   </si>
   <si>
     <t xml:space="preserve">Tahmini Teslim Çıktısı, </t>
+  </si>
+  <si>
+    <t>Görsel olabilir, akış şemaları, tarihsel zaman çizelgesi</t>
+  </si>
+  <si>
+    <t>Teorik açıklama + basit Python veya Qiskit kod örnekleri ile anlatılabilir</t>
+  </si>
+  <si>
+    <t>Bloch küresi temsili görseli anlatılabilir</t>
+  </si>
+  <si>
+    <t>Qiskit devre kodu (.ipynb) + Bloch küresi çıktısı + her kapı ve devre için kısa açıklama</t>
+  </si>
+  <si>
+    <t>Çalışan algoritma kodu (.ipynb) + kod açıklama notları + çıktı ekran görüntüleri</t>
+  </si>
+  <si>
+    <t>Cirq kodu (.ipynb) + kuantum devre şeması (görsel) + açıklama</t>
+  </si>
+  <si>
+    <t>Kurulum rehberi + örnek çalışma kodları</t>
+  </si>
+  <si>
+    <t>Üç algoritmanın örnek kodları (.ipynb)</t>
+  </si>
+  <si>
+    <t>Cirq devre kodu (.ipynb) +  kod açıklama notları + çıktı ekran görüntüleri</t>
+  </si>
+  <si>
+    <t>Q# kod dosyası (.qs) + VS Code ekran görüntüsü + açıklamalar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karşılaştırma raporu  </t>
+  </si>
+  <si>
+    <t>Çalışan algoritma kodu (.ipynb) + uygulama çıktısı + protokol akış şeması</t>
+  </si>
+  <si>
+    <t>Şirin Gülten Çelikaslan</t>
   </si>
 </sst>
 </file>
@@ -655,18 +640,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.54296875" customWidth="1"/>
-    <col min="3" max="3" width="24.7265625" customWidth="1"/>
-    <col min="4" max="4" width="8.984375E-2" customWidth="1"/>
-    <col min="5" max="5" width="55.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="67.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" customWidth="1"/>
+    <col min="5" max="5" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="76.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,13 +668,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -703,10 +688,10 @@
         <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -720,10 +705,10 @@
         <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -737,10 +722,10 @@
         <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -754,10 +739,10 @@
         <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -771,10 +756,10 @@
         <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -788,10 +773,10 @@
         <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -805,10 +790,10 @@
         <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -822,10 +807,10 @@
         <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -839,10 +824,10 @@
         <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -856,10 +841,10 @@
         <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -873,10 +858,10 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -890,10 +875,10 @@
         <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -907,10 +892,10 @@
         <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -924,10 +909,10 @@
         <v>53</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -944,7 +929,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -961,7 +946,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
@@ -975,16 +960,19 @@
         <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
@@ -992,10 +980,10 @@
         <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>8</v>
       </c>
@@ -1009,10 +997,10 @@
         <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1029,10 +1017,10 @@
         <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -1049,10 +1037,10 @@
         <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -1069,7 +1057,7 @@
         <v>61</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
